--- a/data/trans_bre/P57_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P57_R2-Estudios-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,86; -1,78</t>
+          <t>-9,54; -1,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,22; -2,25</t>
+          <t>-11,3; -1,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-38,0; -8,22</t>
+          <t>-36,51; -8,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,02; -7,56</t>
+          <t>-30,6; -4,52</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 0,57</t>
+          <t>-5,34; 0,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,25; -7,06</t>
+          <t>-33,16; -6,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 2,27</t>
+          <t>-16,21; 2,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,62; -14,48</t>
+          <t>-51,0; -12,97</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 1,73</t>
+          <t>-9,49; 1,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 3,41</t>
+          <t>-7,6; 2,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 4,88</t>
+          <t>-22,98; 4,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 7,66</t>
+          <t>-14,79; 6,15</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,27; -1,99</t>
+          <t>-6,27; -1,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,84; -7,02</t>
+          <t>-23,62; -6,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,74; -6,61</t>
+          <t>-19,85; -6,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,43; -14,9</t>
+          <t>-41,9; -13,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P57_R2-Estudios-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-6,6</t>
+          <t>-7,66</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-19,75%</t>
+          <t>-22,6%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,54; -1,94</t>
+          <t>-9,74; -1,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,3; -1,37</t>
+          <t>-12,3; -3,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-36,51; -8,52</t>
+          <t>-38,02; -9,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,6; -4,52</t>
+          <t>-33,43; -11,46</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-15,71</t>
+          <t>-3,38</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-28,43%</t>
+          <t>-6,88%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 0,68</t>
+          <t>-5,26; 0,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,16; -6,46</t>
+          <t>-6,57; -0,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 2,4</t>
+          <t>-16,18; 1,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,0; -12,97</t>
+          <t>-12,9; -0,08</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-2,41</t>
+          <t>-2,94</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-5,04%</t>
+          <t>-6,19%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 1,53</t>
+          <t>-9,85; 1,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 2,76</t>
+          <t>-8,36; 2,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,98; 4,24</t>
+          <t>-24,04; 5,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 6,15</t>
+          <t>-16,65; 5,38</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-12,64</t>
+          <t>-5,08</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-24,95%</t>
+          <t>-10,95%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,27; -1,84</t>
+          <t>-6,37; -1,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,62; -6,25</t>
+          <t>-7,44; -2,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,85; -6,2</t>
+          <t>-20,02; -5,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,9; -13,24</t>
+          <t>-15,52; -5,55</t>
         </is>
       </c>
     </row>
